--- a/data/trans_bre/IP22_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP22_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 10,67</t>
+          <t>-4,07; 10,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 7,09</t>
+          <t>-10,08; 6,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 9,73</t>
+          <t>-5,28; 10,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 10,43</t>
+          <t>-5,63; 11,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-21,7; 83,19</t>
+          <t>-22,07; 79,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-31,91; 35,59</t>
+          <t>-35,72; 32,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-27,41; 68,17</t>
+          <t>-26,03; 81,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-30,77; 101,39</t>
+          <t>-28,44; 113,84</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,87; -0,06</t>
+          <t>-12,86; 0,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 8,22</t>
+          <t>-5,45; 8,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 8,54</t>
+          <t>-2,77; 8,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 15,76</t>
+          <t>0,15; 15,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-43,27; -0,12</t>
+          <t>-42,64; -0,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,94; 33,16</t>
+          <t>-17,48; 39,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,43; 67,76</t>
+          <t>-15,44; 64,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 149,1</t>
+          <t>-3,31; 140,39</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 8,26</t>
+          <t>-8,16; 8,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-23,49; -8,07</t>
+          <t>-23,91; -8,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 9,36</t>
+          <t>-4,31; 10,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 6,4</t>
+          <t>-10,7; 5,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-24,86; 39,14</t>
+          <t>-27,1; 39,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-57,03; -24,6</t>
+          <t>-58,42; -26,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-21,93; 59,11</t>
+          <t>-20,18; 63,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-48,5; 54,68</t>
+          <t>-53,33; 50,12</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 3,25</t>
+          <t>-9,89; 1,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 5,16</t>
+          <t>-8,94; 5,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 2,22</t>
+          <t>-9,1; 2,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,98; -0,68</t>
+          <t>-15,06; -1,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-47,65; 23,16</t>
+          <t>-49,29; 13,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-33,9; 28,69</t>
+          <t>-34,88; 28,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,85; 19,77</t>
+          <t>-49,96; 21,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-65,31; -2,73</t>
+          <t>-66,05; -5,03</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 1,05</t>
+          <t>-5,75; 0,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,6; -0,11</t>
+          <t>-7,8; -0,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 4,08</t>
+          <t>-2,53; 4,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 4,05</t>
+          <t>-3,7; 4,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-26,04; 5,33</t>
+          <t>-25,19; 3,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,64; 0,04</t>
+          <t>-26,5; 0,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 27,05</t>
+          <t>-13,6; 25,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-23,18; 29,0</t>
+          <t>-22,11; 31,36</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP22_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP22_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,51</t>
+          <t>1,8</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 10,85</t>
+          <t>-3,67; 11,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 6,81</t>
+          <t>-10,48; 7,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 10,86</t>
+          <t>-6,33; 9,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 11,97</t>
+          <t>-6,28; 10,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,07; 79,26</t>
+          <t>-18,89; 85,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-35,72; 32,58</t>
+          <t>-34,59; 34,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-26,03; 81,15</t>
+          <t>-30,03; 66,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-28,44; 113,84</t>
+          <t>-32,75; 98,56</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,69</t>
+          <t>4,27</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>33,4%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 0,0</t>
+          <t>-12,79; 0,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 8,97</t>
+          <t>-5,26; 8,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 8,58</t>
+          <t>-2,84; 8,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 15,56</t>
+          <t>-2,42; 10,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-42,64; -0,13</t>
+          <t>-42,41; -0,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-17,48; 39,59</t>
+          <t>-17,73; 36,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,44; 64,51</t>
+          <t>-15,94; 66,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 140,39</t>
+          <t>-15,14; 105,49</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,75</t>
+          <t>2,82</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-5,02%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 8,31</t>
+          <t>-8,25; 8,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-23,91; -8,6</t>
+          <t>-23,95; -8,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 10,21</t>
+          <t>-4,21; 9,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 5,8</t>
+          <t>-5,05; 10,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-27,1; 39,06</t>
+          <t>-28,03; 38,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-58,42; -26,19</t>
+          <t>-59,73; -24,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-20,18; 63,28</t>
+          <t>-18,86; 62,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-53,33; 50,12</t>
+          <t>-26,39; 90,75</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-8,32</t>
+          <t>-8,68</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-43,54%</t>
+          <t>-47,25%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 1,75</t>
+          <t>-9,91; 1,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 5,05</t>
+          <t>-8,39; 5,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 2,43</t>
+          <t>-8,33; 2,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,06; -1,12</t>
+          <t>-15,56; -3,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,29; 13,57</t>
+          <t>-46,9; 15,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-34,88; 28,22</t>
+          <t>-32,47; 30,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,96; 21,61</t>
+          <t>-46,65; 24,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-66,05; -5,03</t>
+          <t>-69,26; -19,54</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,18</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 0,69</t>
+          <t>-5,68; 1,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,8; -0,05</t>
+          <t>-7,63; -0,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 4,04</t>
+          <t>-2,54; 3,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 4,26</t>
+          <t>-3,39; 3,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-25,19; 3,69</t>
+          <t>-23,91; 5,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-26,5; 0,0</t>
+          <t>-26,0; -2,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 25,62</t>
+          <t>-13,56; 25,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-22,11; 31,36</t>
+          <t>-19,9; 23,22</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP22_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP22_R-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -522,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han utilizado las urgencias en el último año</t>
+          <t>Menores que han utilizado  algún servicio de urgencias en los últimos 12 meses</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>3,3</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-1,39</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,13</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,8</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>19,78%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-5,6%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,98%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12,03%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>3.303076041689237</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.393116702340027</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2.134272315977093</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1.797556106886875</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.1978099087649946</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.05601256005812833</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.1198482249271621</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.1203019366764544</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-3,67; 11,39</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-10,48; 7,32</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-6,33; 9,26</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-6,28; 10,41</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-18,89; 85,64</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-34,59; 34,54</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-30,03; 66,07</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-32,75; 98,56</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.666455052631621</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-10.47816071072687</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-6.330069032352529</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-6.280111176133612</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.1889062330841063</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.3458665510526523</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.3002575626708777</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.3275148101632288</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>11.38679796516017</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>7.32129241044569</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>9.25681034451731</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>10.40828037578272</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.8563520149171518</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.3454095648856118</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.6606517385350679</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.9855852363142349</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-6,24</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,4</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,85</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,27</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-23,37%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,06%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>18,17%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>33,4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-12,79; 0,03</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-5,26; 8,34</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-2,84; 8,86</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-2,42; 10,4</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-42,41; -0,17</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-17,73; 36,42</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-15,94; 66,92</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-15,14; 105,49</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-6.243883177285131</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.398137669453242</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>2.854765187104633</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>4.27410716113786</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.2337284354572472</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.0505834069217817</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.1817023086041478</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.3339993783234834</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,25</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-15,81</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,53</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,82</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,95%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-42,78%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>13,03%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>18,71%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-12.79102911161366</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-5.262745420046152</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-2.837337116920488</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-2.415543858827117</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.424081003028897</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.1773465012003625</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.1593581684453757</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.1514372791571685</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-8,25; 8,39</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-23,95; -8,16</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-4,21; 9,76</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-5,05; 10,33</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-28,03; 38,37</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-59,73; -24,9</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-18,86; 62,57</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-26,39; 90,75</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.03451447150571727</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>8.338514091559365</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>8.857509439118445</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>10.40181531334866</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>-0.001706889155412773</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.3641904250500178</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.6692478167633769</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>1.054870690429999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-3,64</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-1,81</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-3,0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-8,68</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-21,41%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-8,22%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-20,13%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-47,25%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.2515978022542387</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-15.81377797573486</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>2.533827766572461</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>2.816470769890425</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.009537773287868437</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.4278159372085049</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.1303099542392149</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.1871290170103446</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-9,91; 1,92</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-8,39; 5,45</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-8,33; 2,57</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-15,56; -3,21</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-46,9; 15,46</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-32,47; 30,22</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-46,65; 24,1</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-69,26; -19,54</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-8.250802920643316</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-23.94551337832045</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.214879086892384</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-5.052507248254609</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.2803022053161335</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.5973074773356906</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.1885530821599589</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.2639421018369211</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>8.390025781048386</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-8.161460562826628</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>9.75679522743131</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>10.32517188868202</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.3837096554669365</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>-0.2489516457947675</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.6257385561085783</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.9074880716021269</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-3.638451765849238</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.811195593581122</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-2.996211112113989</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-8.680938379130508</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.214101880278549</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.08224926037494665</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.201311273210868</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.4725169909106173</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-9.913698514770068</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-8.386387617635343</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-8.331655062867359</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-15.55526099673232</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.4690302138014225</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.324739111748683</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.4665412434569075</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.6925508786544401</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.922548738552184</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>5.446454256254975</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.572803737454866</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>-3.211801369171955</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.1545597404965654</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.3022352036211223</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.2409843409459068</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>-0.1954048805089698</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-2,4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-3,95</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,88</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,18</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-11,02%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-14,34%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,25%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-5,68; 1,12</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-7,63; -0,57</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-2,54; 3,98</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-3,39; 3,12</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-23,91; 5,77</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-26,0; -2,41</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-13,56; 25,72</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-19,9; 23,22</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-2.395243699631203</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-3.951215835661404</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.8793921301998214</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.1784846026985448</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.11023703047662</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.1433537543539037</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.05254208755299705</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.0118429359520068</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-5.683167801245338</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-7.633143900470583</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-2.536614228061019</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-3.394341413295825</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.239099318417747</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.2599869066372418</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.1356287668745965</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.1989651775937161</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.124251567039551</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>-0.5685704669599559</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.97682930800347</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3.122609584085534</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.05770113239555569</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>-0.02406515862058242</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.2572264989565686</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.2321734457508141</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
